--- a/data/processed/case_timeline.xlsx
+++ b/data/processed/case_timeline.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,174 +461,295 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>1999-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杨周武任同乐派出所所长，负责辖区治安和刑事案件办理。</t>
+          <t>舞王歌舞厅（龙平路）获工商许可。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>王静</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>证据5-2</t>
+          <t>缺：原始工商许可</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>舞王歌舞厅发生伤害事件，江军等人受伤并报警。</t>
+          <t>杨周武任同乐派出所所长。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>王静、江军、汪春蓉、赵志高、易承桂</t>
+          <t>杨周武</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>证据1-1、证据1-2</t>
+          <t>缺：任职文件；证据5-2可支撑履职背景</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2006年</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>王静为推动调解和免予刑责，开始筹集资金并联系中间人。</t>
+          <t>舞王歌舞厅（龙平路）被吊销营业执照。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王静、罗宇、陈三一、张夏天</t>
+          <t>王静</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>证据3-2、证据3-3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>核心行贿链</t>
+          <t>缺：吊销营业执照材料</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2007-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>罗宇、陈三一、张夏天将资金转入何晓初及其控制账户。</t>
+          <t>舞王俱乐部（三和村）无许可、换地址开业。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>何晓初、曾黎、饶蝶、周芷</t>
+          <t>王静、赵五</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>证据3-1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>27万元转账</t>
+          <t>证据0-1、证据0-2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2008-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>王静账户取现3万元后，何晓初主账户出现现金存入。</t>
+          <t>舞王俱乐部发生故意伤害案，江军等人受伤并报警。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王静、何晓初</t>
+          <t>江军、汪春蓉、赵志高、罗贤涛、易承桂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>证据3-1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3万元现金链</t>
+          <t>证据1-1、证据1-2、证据1-3、证据1-4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>江军报警</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>办案民警接警</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2008-08-15至2008-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>杨周武安排刘力飚调解，向江军等人支付11万元赔偿款。</t>
+          <t>王静请托并向何晓初送3万元现金。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杨周武、刘力飚、江军、汪春蓉、赵志高、易承桂</t>
+          <t>王静、何晓初、杨周武</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>受贿</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>证据4-1</t>
+          <t>证据3-1、证据3-3、结构化银行流水</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11万元赔偿款</t>
+          <t>3万元现金链</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>王静拨打何晓初/杨周武</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>何晓初/杨周武接听</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2008-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>案件被撤销或作调解处理，相关人员被释放。</t>
+          <t>刘力飚促成11万元赔偿并调解结案。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杨周武、刘力飚</t>
+          <t>杨周武、刘力飚、江军、汪春蓉、赵志高</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>徇私枉法</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>证据4-2、证据2-1</t>
+          <t>证据4-1、结构化银行流水</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11万元赔偿链</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>刘力飚拨打被害方</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>被害方接听</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2008-09-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>舞王俱乐部发生特大火灾，造成44人死亡、64人受伤。</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>王静、舞王俱乐部相关人员</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>玩忽职守</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>证据5-1、证据5-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>事故报警/消防联络</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>杨周武接听事故处置电话</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2008-09-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>深圳市人民检察院对杨周武涉嫌徇私枉法案立案侦查。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>杨周武、深圳市人民检察院</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>徇私枉法</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>证据6-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2008-10-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>杨周武被刑事拘留。</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>杨周武、深圳市人民检察院</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>徇私枉法</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>证据6-2</t>
         </is>
       </c>
     </row>

--- a/data/processed/case_timeline.xlsx
+++ b/data/processed/case_timeline.xlsx
@@ -419,337 +419,337 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>案件事实</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>相关人</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>刑罚</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>相关证据</t>
+          <t>????</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>账目往来流水</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>电话(拨出)</t>
+          <t>??(??)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>电话(接入)</t>
+          <t>??(??)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1999-07-09</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>舞王歌舞厅（龙平路）获工商许可。</t>
+          <t>????????????????</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>缺：原始工商许可</t>
+          <t>????????</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>杨周武任同乐派出所所长。</t>
+          <t>????????????</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>???</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>缺：任职文件；证据5-2可支撑履职背景</t>
+          <t>?????????5-2???????</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006年</t>
+          <t>2022?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>舞王歌舞厅（龙平路）被吊销营业执照。</t>
+          <t>??????????????????</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>缺：吊销营业执照材料</t>
+          <t>??????????</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2007-09-08</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>舞王俱乐部（三和村）无许可、换地址开业。</t>
+          <t>????????????????????</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>王静、赵五</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>证据0-1、证据0-2</t>
+          <t>??0-1???0-2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2008-08-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>舞王俱乐部发生故意伤害案，江军等人受伤并报警。</t>
+          <t>???????????????????????</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>江军、汪春蓉、赵志高、罗贤涛、易承桂</t>
+          <t>??????????????????</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>证据1-1、证据1-2、证据1-3、证据1-4</t>
+          <t>??1-1???1-2???1-3???1-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>江军报警</t>
+          <t>????</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>办案民警接警</t>
+          <t>??????</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2008-08-15至2008-09-05</t>
+          <t>2024-08-15?2024-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>王静请托并向何晓初送3万元现金。</t>
+          <t>??????????3?????</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>王静、何晓初、杨周武</t>
+          <t>??????????</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>受贿</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>证据3-1、证据3-3、结构化银行流水</t>
+          <t>??3-1???3-3????????</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3万元现金链</t>
+          <t>3?????</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>王静拨打何晓初/杨周武</t>
+          <t>???????/???</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>何晓初/杨周武接听</t>
+          <t>???/?????</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2008-09-06</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>刘力飚促成11万元赔偿并调解结案。</t>
+          <t>?????11??????????</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杨周武、刘力飚、江军、汪春蓉、赵志高</t>
+          <t>??????????????????</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>徇私枉法</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>证据4-1、结构化银行流水</t>
+          <t>??4-1????????</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11万元赔偿链</t>
+          <t>11?????</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>刘力飚拨打被害方</t>
+          <t>????????</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>被害方接听</t>
+          <t>?????</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2008-09-20</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>舞王俱乐部发生特大火灾，造成44人死亡、64人受伤。</t>
+          <t>??????????????44????64????</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>王静、舞王俱乐部相关人员</t>
+          <t>????????????</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>玩忽职守</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>证据5-1、证据5-2</t>
+          <t>??5-1???5-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>事故报警/消防联络</t>
+          <t>????/????</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>杨周武接听事故处置电话</t>
+          <t>???????????</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2008-09-28</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>深圳市人民检察院对杨周武涉嫌徇私枉法案立案侦查。</t>
+          <t>????????????????????????</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杨周武、深圳市人民检察院</t>
+          <t>????????????</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>徇私枉法</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>证据6-1</t>
+          <t>??6-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2008-10-25</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>杨周武被刑事拘留。</t>
+          <t>?????????</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杨周武、深圳市人民检察院</t>
+          <t>????????????</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>徇私枉法</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>证据6-2</t>
+          <t>??6-2</t>
         </is>
       </c>
     </row>
